--- a/Docs/Contas.xlsx
+++ b/Docs/Contas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\R\RGitRep\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0F5000-BA65-48C6-853E-2E97BF58C3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD9AE9F-FC24-446C-A4D7-9947C753AD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5805" yWindow="1935" windowWidth="19815" windowHeight="11805" xr2:uid="{C50BC428-7ADB-464C-8292-052325D81446}"/>
   </bookViews>
@@ -39,17 +39,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>Aluguel</t>
   </si>
   <si>
-    <t>Moto</t>
-  </si>
-  <si>
-    <t>Seguro</t>
-  </si>
-  <si>
     <t>Pensão</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
     <t>Saldo real</t>
   </si>
   <si>
-    <t>Reccorrentes</t>
-  </si>
-  <si>
     <t>Grão Gourmet</t>
   </si>
   <si>
@@ -150,6 +141,45 @@
   </si>
   <si>
     <t>Tarifa banco</t>
+  </si>
+  <si>
+    <t>Revisão moto</t>
+  </si>
+  <si>
+    <t>Passagem Aerea</t>
+  </si>
+  <si>
+    <t>Relogio</t>
+  </si>
+  <si>
+    <t>Rampa moto</t>
+  </si>
+  <si>
+    <t>Bota moto</t>
+  </si>
+  <si>
+    <t>Sofa</t>
+  </si>
+  <si>
+    <t>TV</t>
+  </si>
+  <si>
+    <t>Regua Sinalização</t>
+  </si>
+  <si>
+    <t>Rampa moto aux</t>
+  </si>
+  <si>
+    <t>Capa chuva</t>
+  </si>
+  <si>
+    <t>Recorrentes</t>
+  </si>
+  <si>
+    <t>Financ. Moto</t>
+  </si>
+  <si>
+    <t>Seguro Moto</t>
   </si>
 </sst>
 </file>
@@ -209,7 +239,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -218,17 +248,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -428,8 +447,47 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -440,45 +498,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -816,63 +877,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85C0CCA-2B2A-4CAB-BBA8-DC21A77D5C0E}">
-  <dimension ref="B1:P23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="16" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B1" s="20" t="s">
+    <row r="1" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18" t="s">
+      <c r="F1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="J1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="17" t="s">
+      <c r="K1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="L1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="M1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="N1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="O1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="P1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="Q1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="P1" s="19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+    </row>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="4">
@@ -885,30 +948,33 @@
       <c r="E2" s="4">
         <v>21000</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="19">
         <f>E2-D2</f>
         <v>3977.5499999999993</v>
       </c>
-      <c r="G2" s="23"/>
-      <c r="H2" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="4">
-        <v>35</v>
+      <c r="G2" s="32"/>
+      <c r="H2" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>43</v>
       </c>
       <c r="J2" s="4">
         <v>35</v>
       </c>
-      <c r="K2" s="4"/>
+      <c r="K2" s="4">
+        <v>35</v>
+      </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
-      <c r="P2" s="5"/>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
-        <v>1</v>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="5"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="C3" s="4">
         <v>1450</v>
@@ -916,24 +982,27 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="4">
-        <v>300</v>
+      <c r="G3" s="32"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="30" t="s">
+        <v>34</v>
       </c>
       <c r="J3" s="4">
         <v>300</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="K3" s="4">
+        <v>300</v>
+      </c>
+      <c r="L3" s="19"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
-      <c r="P3" s="5"/>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
-        <v>2</v>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="5"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="C4" s="4">
         <v>170</v>
@@ -941,22 +1010,25 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="4">
+      <c r="G4" s="32"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="4">
         <v>95</v>
       </c>
-      <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
-        <v>3</v>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="5"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>1</v>
       </c>
       <c r="C5" s="4">
         <v>4150.45</v>
@@ -964,10 +1036,10 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="4">
-        <v>40</v>
+      <c r="G5" s="32"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="J5" s="4">
         <v>40</v>
@@ -975,15 +1047,18 @@
       <c r="K5" s="4">
         <v>40</v>
       </c>
-      <c r="L5" s="4"/>
+      <c r="L5" s="4">
+        <v>40</v>
+      </c>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
-      <c r="P5" s="5"/>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
-        <v>4</v>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="5"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>2</v>
       </c>
       <c r="C6" s="4">
         <v>2000</v>
@@ -991,10 +1066,10 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="4">
-        <v>155</v>
+      <c r="G6" s="32"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="J6" s="4">
         <v>155</v>
@@ -1014,11 +1089,14 @@
       <c r="O6" s="4">
         <v>155</v>
       </c>
-      <c r="P6" s="5"/>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>5</v>
+      <c r="P6" s="4">
+        <v>155</v>
+      </c>
+      <c r="Q6" s="26"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>3</v>
       </c>
       <c r="C7" s="4">
         <v>1040</v>
@@ -1026,22 +1104,25 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="4">
+      <c r="G7" s="32"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="4">
         <v>198</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="19"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
-      <c r="P7" s="5"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
-        <v>6</v>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="C8" s="4">
         <v>750</v>
@@ -1049,24 +1130,27 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="4">
-        <v>466</v>
+      <c r="G8" s="32"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="30" t="s">
+        <v>35</v>
       </c>
       <c r="J8" s="4">
         <v>466</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="K8" s="4">
+        <v>466</v>
+      </c>
+      <c r="L8" s="19"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
-      <c r="P8" s="5"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
-        <v>7</v>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>5</v>
       </c>
       <c r="C9" s="4">
         <v>280</v>
@@ -1074,10 +1158,10 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="4">
-        <v>137</v>
+      <c r="G9" s="32"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="30" t="s">
+        <v>38</v>
       </c>
       <c r="J9" s="4">
         <v>137</v>
@@ -1088,14 +1172,17 @@
       <c r="L9" s="4">
         <v>137</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
+      <c r="M9" s="4">
+        <v>137</v>
+      </c>
+      <c r="N9" s="19"/>
       <c r="O9" s="4"/>
-      <c r="P9" s="5"/>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
-        <v>8</v>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>6</v>
       </c>
       <c r="C10" s="4">
         <v>400</v>
@@ -1103,10 +1190,10 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="4">
-        <v>190</v>
+      <c r="G10" s="32"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="30" t="s">
+        <v>39</v>
       </c>
       <c r="J10" s="4">
         <v>190</v>
@@ -1126,11 +1213,14 @@
       <c r="O10" s="4">
         <v>190</v>
       </c>
-      <c r="P10" s="5"/>
-    </row>
-    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="9" t="s">
-        <v>9</v>
+      <c r="P10" s="4">
+        <v>190</v>
+      </c>
+      <c r="Q10" s="26"/>
+    </row>
+    <row r="11" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="C11" s="4">
         <v>3300</v>
@@ -1138,10 +1228,10 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="6">
-        <v>190</v>
+      <c r="G11" s="32"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="31" t="s">
+        <v>40</v>
       </c>
       <c r="J11" s="6">
         <v>190</v>
@@ -1161,11 +1251,14 @@
       <c r="O11" s="6">
         <v>190</v>
       </c>
-      <c r="P11" s="7"/>
-    </row>
-    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="9" t="s">
-        <v>35</v>
+      <c r="P11" s="6">
+        <v>190</v>
+      </c>
+      <c r="Q11" s="27"/>
+    </row>
+    <row r="12" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="C12" s="4">
         <v>210</v>
@@ -1173,25 +1266,26 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="29">
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="24">
         <f>118+796</f>
         <v>914</v>
       </c>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="30"/>
-    </row>
-    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="9" t="s">
-        <v>36</v>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="25"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="C13" s="4">
         <v>72</v>
@@ -1199,388 +1293,400 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="5"/>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="25"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="8" t="s">
+      <c r="G13" s="32"/>
+      <c r="H13" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="2">
+        <v>63</v>
+      </c>
+      <c r="K13" s="2">
+        <v>63</v>
+      </c>
+      <c r="L13" s="2">
+        <v>63</v>
+      </c>
+      <c r="M13" s="2">
+        <v>63</v>
+      </c>
+      <c r="N13" s="2">
+        <v>63</v>
+      </c>
+      <c r="O13" s="2">
+        <v>63</v>
+      </c>
+      <c r="P13" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="4">
+        <v>60</v>
+      </c>
+      <c r="K14" s="4">
+        <v>60</v>
+      </c>
+      <c r="L14" s="4">
+        <v>60</v>
+      </c>
+      <c r="M14" s="4">
+        <v>60</v>
+      </c>
+      <c r="N14" s="4">
+        <v>60</v>
+      </c>
+      <c r="O14" s="4">
+        <v>60</v>
+      </c>
+      <c r="P14" s="4">
+        <v>60</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B15" s="20"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="4">
+        <v>96</v>
+      </c>
+      <c r="K15" s="4">
+        <v>96</v>
+      </c>
+      <c r="L15" s="4">
+        <v>96</v>
+      </c>
+      <c r="M15" s="4">
+        <v>96</v>
+      </c>
+      <c r="N15" s="4">
+        <v>96</v>
+      </c>
+      <c r="O15" s="4">
+        <v>96</v>
+      </c>
+      <c r="P15" s="4">
+        <v>96</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B16" s="20"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="4">
+        <v>45</v>
+      </c>
+      <c r="K16" s="4">
+        <v>45</v>
+      </c>
+      <c r="L16" s="4">
+        <v>45</v>
+      </c>
+      <c r="M16" s="4">
+        <v>45</v>
+      </c>
+      <c r="N16" s="4">
+        <v>45</v>
+      </c>
+      <c r="O16" s="4">
+        <v>45</v>
+      </c>
+      <c r="P16" s="4">
+        <v>45</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B17" s="20"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="2">
-        <v>63</v>
-      </c>
-      <c r="J14" s="2">
-        <v>63</v>
-      </c>
-      <c r="K14" s="2">
-        <v>63</v>
-      </c>
-      <c r="L14" s="2">
-        <v>63</v>
-      </c>
-      <c r="M14" s="2">
-        <v>63</v>
-      </c>
-      <c r="N14" s="2">
-        <v>63</v>
-      </c>
-      <c r="O14" s="2">
-        <v>63</v>
-      </c>
-      <c r="P14" s="3">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="25"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="4">
-        <v>60</v>
-      </c>
-      <c r="J15" s="4">
-        <v>60</v>
-      </c>
-      <c r="K15" s="4">
-        <v>60</v>
-      </c>
-      <c r="L15" s="4">
-        <v>60</v>
-      </c>
-      <c r="M15" s="4">
-        <v>60</v>
-      </c>
-      <c r="N15" s="4">
-        <v>60</v>
-      </c>
-      <c r="O15" s="4">
-        <v>60</v>
-      </c>
-      <c r="P15" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B16" s="25"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="4">
-        <v>96</v>
-      </c>
-      <c r="J16" s="4">
-        <v>96</v>
-      </c>
-      <c r="K16" s="4">
-        <v>96</v>
-      </c>
-      <c r="L16" s="4">
-        <v>96</v>
-      </c>
-      <c r="M16" s="4">
-        <v>96</v>
-      </c>
-      <c r="N16" s="4">
-        <v>96</v>
-      </c>
-      <c r="O16" s="4">
-        <v>96</v>
-      </c>
-      <c r="P16" s="5">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B17" s="25"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="9" t="s">
+      <c r="J17" s="4">
+        <v>25</v>
+      </c>
+      <c r="K17" s="4">
+        <v>25</v>
+      </c>
+      <c r="L17" s="4">
+        <v>25</v>
+      </c>
+      <c r="M17" s="4">
+        <v>25</v>
+      </c>
+      <c r="N17" s="4">
+        <v>25</v>
+      </c>
+      <c r="O17" s="4">
+        <v>25</v>
+      </c>
+      <c r="P17" s="4">
+        <v>25</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B18" s="20"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="I17" s="4">
-        <v>45</v>
-      </c>
-      <c r="J17" s="4">
-        <v>45</v>
-      </c>
-      <c r="K17" s="4">
-        <v>45</v>
-      </c>
-      <c r="L17" s="4">
-        <v>45</v>
-      </c>
-      <c r="M17" s="4">
-        <v>45</v>
-      </c>
-      <c r="N17" s="4">
-        <v>45</v>
-      </c>
-      <c r="O17" s="4">
-        <v>45</v>
-      </c>
-      <c r="P17" s="5">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B18" s="25"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="9" t="s">
+      <c r="J18" s="4">
+        <v>24</v>
+      </c>
+      <c r="K18" s="4">
+        <v>24</v>
+      </c>
+      <c r="L18" s="4">
+        <v>24</v>
+      </c>
+      <c r="M18" s="4">
+        <v>24</v>
+      </c>
+      <c r="N18" s="4">
+        <v>24</v>
+      </c>
+      <c r="O18" s="4">
+        <v>24</v>
+      </c>
+      <c r="P18" s="4">
+        <v>24</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B19" s="20"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="4">
-        <v>25</v>
-      </c>
-      <c r="J18" s="4">
-        <v>25</v>
-      </c>
-      <c r="K18" s="4">
-        <v>25</v>
-      </c>
-      <c r="L18" s="4">
-        <v>25</v>
-      </c>
-      <c r="M18" s="4">
-        <v>25</v>
-      </c>
-      <c r="N18" s="4">
-        <v>25</v>
-      </c>
-      <c r="O18" s="4">
-        <v>25</v>
-      </c>
-      <c r="P18" s="5">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="25"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="9" t="s">
+      <c r="J19" s="4">
+        <v>41</v>
+      </c>
+      <c r="K19" s="4">
+        <v>41</v>
+      </c>
+      <c r="L19" s="4">
+        <v>41</v>
+      </c>
+      <c r="M19" s="4">
+        <v>41</v>
+      </c>
+      <c r="N19" s="4">
+        <v>41</v>
+      </c>
+      <c r="O19" s="4">
+        <v>41</v>
+      </c>
+      <c r="P19" s="4">
+        <v>41</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="20"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="4">
-        <v>24</v>
-      </c>
-      <c r="J19" s="4">
-        <v>24</v>
-      </c>
-      <c r="K19" s="4">
-        <v>24</v>
-      </c>
-      <c r="L19" s="4">
-        <v>24</v>
-      </c>
-      <c r="M19" s="4">
-        <v>24</v>
-      </c>
-      <c r="N19" s="4">
-        <v>24</v>
-      </c>
-      <c r="O19" s="4">
-        <v>24</v>
-      </c>
-      <c r="P19" s="5">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B20" s="25"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="9" t="s">
+      <c r="J20" s="6">
         <v>27</v>
       </c>
-      <c r="I20" s="4">
-        <v>41</v>
-      </c>
-      <c r="J20" s="4">
-        <v>41</v>
-      </c>
-      <c r="K20" s="4">
-        <v>41</v>
-      </c>
-      <c r="L20" s="4">
-        <v>41</v>
-      </c>
-      <c r="M20" s="4">
-        <v>41</v>
-      </c>
-      <c r="N20" s="4">
-        <v>41</v>
-      </c>
-      <c r="O20" s="4">
-        <v>41</v>
-      </c>
-      <c r="P20" s="5">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="25"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="10" t="s">
+      <c r="K20" s="6">
+        <v>27</v>
+      </c>
+      <c r="L20" s="6">
+        <v>27</v>
+      </c>
+      <c r="M20" s="6">
+        <v>27</v>
+      </c>
+      <c r="N20" s="6">
+        <v>27</v>
+      </c>
+      <c r="O20" s="6">
+        <v>27</v>
+      </c>
+      <c r="P20" s="6">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B21" s="20"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="10">
+        <f>SUM(J2:J20)</f>
+        <v>3101</v>
+      </c>
+      <c r="K21" s="10">
+        <f>SUM(K2:K20)</f>
+        <v>1894</v>
+      </c>
+      <c r="L21" s="10">
+        <f>SUM(L2:L20)</f>
+        <v>1093</v>
+      </c>
+      <c r="M21" s="10">
+        <f>SUM(M2:M20)</f>
+        <v>1053</v>
+      </c>
+      <c r="N21" s="10">
+        <f>SUM(N2:N20)</f>
+        <v>916</v>
+      </c>
+      <c r="O21" s="10">
+        <f>SUM(O2:O20)</f>
+        <v>916</v>
+      </c>
+      <c r="P21" s="10">
+        <f>SUM(P2:P20)</f>
+        <v>916</v>
+      </c>
+      <c r="Q21" s="11">
+        <f>SUM(Q2:Q20)</f>
+        <v>381</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="6">
-        <v>27</v>
-      </c>
-      <c r="J21" s="6">
-        <v>27</v>
-      </c>
-      <c r="K21" s="6">
-        <v>27</v>
-      </c>
-      <c r="L21" s="6">
-        <v>27</v>
-      </c>
-      <c r="M21" s="6">
-        <v>27</v>
-      </c>
-      <c r="N21" s="6">
-        <v>27</v>
-      </c>
-      <c r="O21" s="6">
-        <v>27</v>
-      </c>
-      <c r="P21" s="7">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B22" s="25"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="12">
-        <f>SUM(I2:I21)</f>
-        <v>3101</v>
-      </c>
-      <c r="J22" s="12">
-        <f t="shared" ref="J22:P22" si="0">SUM(J2:J21)</f>
-        <v>1894</v>
-      </c>
-      <c r="K22" s="12">
+      <c r="J22" s="13">
+        <f>$F$2-J21</f>
+        <v>876.54999999999927</v>
+      </c>
+      <c r="K22" s="13">
+        <f t="shared" ref="K22:Q22" si="0">$F$2-K21</f>
+        <v>2083.5499999999993</v>
+      </c>
+      <c r="L22" s="13">
         <f t="shared" si="0"/>
-        <v>1093</v>
-      </c>
-      <c r="L22" s="12">
+        <v>2884.5499999999993</v>
+      </c>
+      <c r="M22" s="13">
         <f t="shared" si="0"/>
-        <v>1053</v>
-      </c>
-      <c r="M22" s="12">
+        <v>2924.5499999999993</v>
+      </c>
+      <c r="N22" s="13">
         <f t="shared" si="0"/>
-        <v>916</v>
-      </c>
-      <c r="N22" s="12">
+        <v>3061.5499999999993</v>
+      </c>
+      <c r="O22" s="13">
         <f t="shared" si="0"/>
-        <v>916</v>
-      </c>
-      <c r="O22" s="12">
-        <f t="shared" si="0"/>
-        <v>916</v>
+        <v>3061.5499999999993</v>
       </c>
       <c r="P22" s="13">
         <f t="shared" si="0"/>
-        <v>381</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="26"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" s="15">
-        <f>$F$2-I22</f>
-        <v>876.54999999999927</v>
-      </c>
-      <c r="J23" s="15">
-        <f t="shared" ref="J23:P23" si="1">$F$2-J22</f>
-        <v>2083.5499999999993</v>
-      </c>
-      <c r="K23" s="15">
-        <f t="shared" si="1"/>
-        <v>2884.5499999999993</v>
-      </c>
-      <c r="L23" s="15">
-        <f t="shared" si="1"/>
-        <v>2924.5499999999993</v>
-      </c>
-      <c r="M23" s="15">
-        <f t="shared" si="1"/>
         <v>3061.5499999999993</v>
       </c>
-      <c r="N23" s="15">
-        <f t="shared" si="1"/>
-        <v>3061.5499999999993</v>
-      </c>
-      <c r="O23" s="15">
-        <f t="shared" si="1"/>
-        <v>3061.5499999999993</v>
-      </c>
-      <c r="P23" s="16">
-        <f t="shared" si="1"/>
+      <c r="Q22" s="14">
+        <f t="shared" si="0"/>
         <v>3596.5499999999993</v>
       </c>
     </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="32"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="32"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="H2:H11"/>
+    <mergeCell ref="H13:H20"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Docs/Contas.xlsx
+++ b/Docs/Contas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\R\RGitRep\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD9AE9F-FC24-446C-A4D7-9947C753AD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF08616D-83E1-4085-A1C0-9901A745B1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5805" yWindow="1935" windowWidth="19815" windowHeight="11805" xr2:uid="{C50BC428-7ADB-464C-8292-052325D81446}"/>
   </bookViews>
@@ -498,7 +498,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -531,8 +531,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -877,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85C0CCA-2B2A-4CAB-BBA8-DC21A77D5C0E}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="B1:Q22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -943,17 +941,16 @@
       </c>
       <c r="D2" s="4">
         <f>SUM(C:C)</f>
-        <v>17022.45</v>
+        <v>17042.45</v>
       </c>
       <c r="E2" s="4">
         <v>21000</v>
       </c>
       <c r="F2" s="19">
         <f>E2-D2</f>
-        <v>3977.5499999999993</v>
-      </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="34" t="s">
+        <v>3957.5499999999993</v>
+      </c>
+      <c r="H2" s="32" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="29" t="s">
@@ -982,8 +979,7 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="35"/>
+      <c r="H3" s="33"/>
       <c r="I3" s="30" t="s">
         <v>34</v>
       </c>
@@ -1010,8 +1006,7 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="35"/>
+      <c r="H4" s="33"/>
       <c r="I4" s="30" t="s">
         <v>42</v>
       </c>
@@ -1036,8 +1031,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="35"/>
+      <c r="H5" s="33"/>
       <c r="I5" s="30" t="s">
         <v>41</v>
       </c>
@@ -1066,8 +1060,7 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="35"/>
+      <c r="H6" s="33"/>
       <c r="I6" s="30" t="s">
         <v>36</v>
       </c>
@@ -1104,8 +1097,7 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="35"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="30" t="s">
         <v>37</v>
       </c>
@@ -1130,8 +1122,7 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="35"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="30" t="s">
         <v>35</v>
       </c>
@@ -1153,13 +1144,12 @@
         <v>5</v>
       </c>
       <c r="C9" s="4">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="35"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="30" t="s">
         <v>38</v>
       </c>
@@ -1190,8 +1180,7 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="35"/>
+      <c r="H10" s="33"/>
       <c r="I10" s="30" t="s">
         <v>39</v>
       </c>
@@ -1228,8 +1217,7 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="36"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="31" t="s">
         <v>40</v>
       </c>
@@ -1266,14 +1254,12 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
       <c r="I12" s="23" t="s">
         <v>30</v>
       </c>
       <c r="J12" s="24">
-        <f>118+796</f>
-        <v>914</v>
+        <f>118+796+66+30</f>
+        <v>1010</v>
       </c>
       <c r="K12" s="24"/>
       <c r="L12" s="24"/>
@@ -1293,8 +1279,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="34" t="s">
+      <c r="H13" s="32" t="s">
         <v>44</v>
       </c>
       <c r="I13" s="29" t="s">
@@ -1327,12 +1312,7 @@
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="20"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="35"/>
+      <c r="H14" s="33"/>
       <c r="I14" s="30" t="s">
         <v>20</v>
       </c>
@@ -1363,12 +1343,7 @@
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="20"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="35"/>
+      <c r="H15" s="33"/>
       <c r="I15" s="30" t="s">
         <v>29</v>
       </c>
@@ -1399,12 +1374,7 @@
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="20"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="35"/>
+      <c r="H16" s="33"/>
       <c r="I16" s="30" t="s">
         <v>22</v>
       </c>
@@ -1433,14 +1403,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="20"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="35"/>
+      <c r="H17" s="33"/>
       <c r="I17" s="30" t="s">
         <v>23</v>
       </c>
@@ -1469,14 +1434,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="20"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="35"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="30" t="s">
         <v>24</v>
       </c>
@@ -1505,14 +1465,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="20"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="35"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="30" t="s">
         <v>25</v>
       </c>
@@ -1541,14 +1496,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="20"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="36"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="31" t="s">
         <v>26</v>
       </c>
@@ -1577,51 +1527,45 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="20"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
       <c r="I21" s="9" t="s">
         <v>9</v>
       </c>
       <c r="J21" s="10">
-        <f>SUM(J2:J20)</f>
-        <v>3101</v>
+        <f t="shared" ref="J21:Q21" si="0">SUM(J2:J20)</f>
+        <v>3197</v>
       </c>
       <c r="K21" s="10">
-        <f>SUM(K2:K20)</f>
+        <f t="shared" si="0"/>
         <v>1894</v>
       </c>
       <c r="L21" s="10">
-        <f>SUM(L2:L20)</f>
+        <f t="shared" si="0"/>
         <v>1093</v>
       </c>
       <c r="M21" s="10">
-        <f>SUM(M2:M20)</f>
+        <f t="shared" si="0"/>
         <v>1053</v>
       </c>
       <c r="N21" s="10">
-        <f>SUM(N2:N20)</f>
+        <f t="shared" si="0"/>
         <v>916</v>
       </c>
       <c r="O21" s="10">
-        <f>SUM(O2:O20)</f>
+        <f t="shared" si="0"/>
         <v>916</v>
       </c>
       <c r="P21" s="10">
-        <f>SUM(P2:P20)</f>
+        <f t="shared" si="0"/>
         <v>916</v>
       </c>
       <c r="Q21" s="11">
-        <f>SUM(Q2:Q20)</f>
+        <f t="shared" si="0"/>
         <v>381</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="21"/>
       <c r="C22" s="22"/>
       <c r="D22" s="22"/>
@@ -1634,54 +1578,36 @@
       </c>
       <c r="J22" s="13">
         <f>$F$2-J21</f>
-        <v>876.54999999999927</v>
+        <v>760.54999999999927</v>
       </c>
       <c r="K22" s="13">
-        <f t="shared" ref="K22:Q22" si="0">$F$2-K21</f>
-        <v>2083.5499999999993</v>
+        <f t="shared" ref="K22:Q22" si="1">$F$2-K21</f>
+        <v>2063.5499999999993</v>
       </c>
       <c r="L22" s="13">
-        <f t="shared" si="0"/>
-        <v>2884.5499999999993</v>
+        <f t="shared" si="1"/>
+        <v>2864.5499999999993</v>
       </c>
       <c r="M22" s="13">
-        <f t="shared" si="0"/>
-        <v>2924.5499999999993</v>
+        <f t="shared" si="1"/>
+        <v>2904.5499999999993</v>
       </c>
       <c r="N22" s="13">
-        <f t="shared" si="0"/>
-        <v>3061.5499999999993</v>
+        <f t="shared" si="1"/>
+        <v>3041.5499999999993</v>
       </c>
       <c r="O22" s="13">
-        <f t="shared" si="0"/>
-        <v>3061.5499999999993</v>
+        <f t="shared" si="1"/>
+        <v>3041.5499999999993</v>
       </c>
       <c r="P22" s="13">
-        <f t="shared" si="0"/>
-        <v>3061.5499999999993</v>
+        <f t="shared" si="1"/>
+        <v>3041.5499999999993</v>
       </c>
       <c r="Q22" s="14">
-        <f t="shared" si="0"/>
-        <v>3596.5499999999993</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
+        <f t="shared" si="1"/>
+        <v>3576.5499999999993</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Docs/Contas.xlsx
+++ b/Docs/Contas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\R\RGitRep\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\RGitRep\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD9AE9F-FC24-446C-A4D7-9947C753AD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C231EF-E8BD-474D-83D6-D8318F61E46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5805" yWindow="1935" windowWidth="19815" windowHeight="11805" xr2:uid="{C50BC428-7ADB-464C-8292-052325D81446}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C50BC428-7ADB-464C-8292-052325D81446}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -498,7 +498,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -531,8 +531,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -877,20 +875,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85C0CCA-2B2A-4CAB-BBA8-DC21A77D5C0E}">
-  <dimension ref="A1:Q24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:Q22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="17" t="s">
         <v>8</v>
       </c>
@@ -934,7 +932,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
@@ -943,17 +941,16 @@
       </c>
       <c r="D2" s="4">
         <f>SUM(C:C)</f>
-        <v>17022.45</v>
+        <v>17042.45</v>
       </c>
       <c r="E2" s="4">
         <v>21000</v>
       </c>
       <c r="F2" s="19">
         <f>E2-D2</f>
-        <v>3977.5499999999993</v>
-      </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="34" t="s">
+        <v>3957.5499999999993</v>
+      </c>
+      <c r="H2" s="32" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="29" t="s">
@@ -972,7 +969,7 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="5"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" s="8" t="s">
         <v>45</v>
       </c>
@@ -982,8 +979,7 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="35"/>
+      <c r="H3" s="33"/>
       <c r="I3" s="30" t="s">
         <v>34</v>
       </c>
@@ -1000,7 +996,7 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="5"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>46</v>
       </c>
@@ -1010,8 +1006,7 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="35"/>
+      <c r="H4" s="33"/>
       <c r="I4" s="30" t="s">
         <v>42</v>
       </c>
@@ -1026,7 +1021,7 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
         <v>1</v>
       </c>
@@ -1036,8 +1031,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="35"/>
+      <c r="H5" s="33"/>
       <c r="I5" s="30" t="s">
         <v>41</v>
       </c>
@@ -1056,7 +1050,7 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
@@ -1066,8 +1060,7 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="35"/>
+      <c r="H6" s="33"/>
       <c r="I6" s="30" t="s">
         <v>36</v>
       </c>
@@ -1094,7 +1087,7 @@
       </c>
       <c r="Q6" s="26"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1097,7 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="35"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="30" t="s">
         <v>37</v>
       </c>
@@ -1120,7 +1112,7 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>4</v>
       </c>
@@ -1130,8 +1122,7 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="35"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="30" t="s">
         <v>35</v>
       </c>
@@ -1148,18 +1139,17 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="8" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="4">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="35"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="30" t="s">
         <v>38</v>
       </c>
@@ -1180,7 +1170,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>6</v>
       </c>
@@ -1190,8 +1180,7 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="35"/>
+      <c r="H10" s="33"/>
       <c r="I10" s="30" t="s">
         <v>39</v>
       </c>
@@ -1218,7 +1207,7 @@
       </c>
       <c r="Q10" s="26"/>
     </row>
-    <row r="11" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
@@ -1228,8 +1217,7 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="36"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="31" t="s">
         <v>40</v>
       </c>
@@ -1256,7 +1244,7 @@
       </c>
       <c r="Q11" s="27"/>
     </row>
-    <row r="12" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="8" t="s">
         <v>32</v>
       </c>
@@ -1266,14 +1254,12 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
       <c r="I12" s="23" t="s">
         <v>30</v>
       </c>
       <c r="J12" s="24">
-        <f>118+796</f>
-        <v>914</v>
+        <f>118+796+66</f>
+        <v>980</v>
       </c>
       <c r="K12" s="24"/>
       <c r="L12" s="24"/>
@@ -1283,7 +1269,7 @@
       <c r="P12" s="24"/>
       <c r="Q12" s="25"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="8" t="s">
         <v>33</v>
       </c>
@@ -1293,8 +1279,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="34" t="s">
+      <c r="H13" s="32" t="s">
         <v>44</v>
       </c>
       <c r="I13" s="29" t="s">
@@ -1325,14 +1310,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="20"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="35"/>
+      <c r="H14" s="33"/>
       <c r="I14" s="30" t="s">
         <v>20</v>
       </c>
@@ -1361,14 +1341,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="20"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="35"/>
+      <c r="H15" s="33"/>
       <c r="I15" s="30" t="s">
         <v>29</v>
       </c>
@@ -1397,14 +1372,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" s="20"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="35"/>
+      <c r="H16" s="33"/>
       <c r="I16" s="30" t="s">
         <v>22</v>
       </c>
@@ -1433,14 +1403,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" s="20"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="35"/>
+      <c r="H17" s="33"/>
       <c r="I17" s="30" t="s">
         <v>23</v>
       </c>
@@ -1469,14 +1434,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" s="20"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="35"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="30" t="s">
         <v>24</v>
       </c>
@@ -1505,14 +1465,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="20"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="35"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="30" t="s">
         <v>25</v>
       </c>
@@ -1541,14 +1496,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="20"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="36"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="31" t="s">
         <v>26</v>
       </c>
@@ -1577,51 +1527,45 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" s="20"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
       <c r="I21" s="9" t="s">
         <v>9</v>
       </c>
       <c r="J21" s="10">
-        <f>SUM(J2:J20)</f>
-        <v>3101</v>
+        <f t="shared" ref="J21:Q21" si="0">SUM(J2:J20)</f>
+        <v>3167</v>
       </c>
       <c r="K21" s="10">
-        <f>SUM(K2:K20)</f>
+        <f t="shared" si="0"/>
         <v>1894</v>
       </c>
       <c r="L21" s="10">
-        <f>SUM(L2:L20)</f>
+        <f t="shared" si="0"/>
         <v>1093</v>
       </c>
       <c r="M21" s="10">
-        <f>SUM(M2:M20)</f>
+        <f t="shared" si="0"/>
         <v>1053</v>
       </c>
       <c r="N21" s="10">
-        <f>SUM(N2:N20)</f>
+        <f t="shared" si="0"/>
         <v>916</v>
       </c>
       <c r="O21" s="10">
-        <f>SUM(O2:O20)</f>
+        <f t="shared" si="0"/>
         <v>916</v>
       </c>
       <c r="P21" s="10">
-        <f>SUM(P2:P20)</f>
+        <f t="shared" si="0"/>
         <v>916</v>
       </c>
       <c r="Q21" s="11">
-        <f>SUM(Q2:Q20)</f>
+        <f t="shared" si="0"/>
         <v>381</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="21"/>
       <c r="C22" s="22"/>
       <c r="D22" s="22"/>
@@ -1634,54 +1578,36 @@
       </c>
       <c r="J22" s="13">
         <f>$F$2-J21</f>
-        <v>876.54999999999927</v>
+        <v>790.54999999999927</v>
       </c>
       <c r="K22" s="13">
-        <f t="shared" ref="K22:Q22" si="0">$F$2-K21</f>
-        <v>2083.5499999999993</v>
+        <f t="shared" ref="K22:Q22" si="1">$F$2-K21</f>
+        <v>2063.5499999999993</v>
       </c>
       <c r="L22" s="13">
-        <f t="shared" si="0"/>
-        <v>2884.5499999999993</v>
+        <f t="shared" si="1"/>
+        <v>2864.5499999999993</v>
       </c>
       <c r="M22" s="13">
-        <f t="shared" si="0"/>
-        <v>2924.5499999999993</v>
+        <f t="shared" si="1"/>
+        <v>2904.5499999999993</v>
       </c>
       <c r="N22" s="13">
-        <f t="shared" si="0"/>
-        <v>3061.5499999999993</v>
+        <f t="shared" si="1"/>
+        <v>3041.5499999999993</v>
       </c>
       <c r="O22" s="13">
-        <f t="shared" si="0"/>
-        <v>3061.5499999999993</v>
+        <f t="shared" si="1"/>
+        <v>3041.5499999999993</v>
       </c>
       <c r="P22" s="13">
-        <f t="shared" si="0"/>
-        <v>3061.5499999999993</v>
+        <f t="shared" si="1"/>
+        <v>3041.5499999999993</v>
       </c>
       <c r="Q22" s="14">
-        <f t="shared" si="0"/>
-        <v>3596.5499999999993</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
+        <f t="shared" si="1"/>
+        <v>3576.5499999999993</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
